--- a/templates/waiting_data.xlsx
+++ b/templates/waiting_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALOSTATH\Desktop\Waiting\نسخ ملفات اكسل\المتنبي\النسخة\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALOSTATH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{620CF177-1CBE-45F7-ADB2-411F4B76A0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136C8E3D-FF21-45C1-A9D6-8EC247064C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maininfo" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="44">
   <si>
     <t xml:space="preserve">إدارة التعليم </t>
   </si>
@@ -48,228 +48,6 @@
     <t xml:space="preserve">رقم الجوال </t>
   </si>
   <si>
-    <t>1093773065</t>
-  </si>
-  <si>
-    <t>عبدالله مسلم سلوم العوفي</t>
-  </si>
-  <si>
-    <t>966544396767</t>
-  </si>
-  <si>
-    <t>1026336915</t>
-  </si>
-  <si>
-    <t>عبدالهادي حمد مطلق الركاد</t>
-  </si>
-  <si>
-    <t>966583565555</t>
-  </si>
-  <si>
-    <t>1075515864</t>
-  </si>
-  <si>
-    <t>عتيق مطلق عتيق الشمري</t>
-  </si>
-  <si>
-    <t>966506187454</t>
-  </si>
-  <si>
-    <t>1105311052</t>
-  </si>
-  <si>
-    <t>عيد سرور معتوق السلامه</t>
-  </si>
-  <si>
-    <t>966560958185</t>
-  </si>
-  <si>
-    <t>1014001729</t>
-  </si>
-  <si>
-    <t>فارس علي ناصر السرور</t>
-  </si>
-  <si>
-    <t>966506184751</t>
-  </si>
-  <si>
-    <t>1015853300</t>
-  </si>
-  <si>
-    <t>فريح صالح فريح اللحيدان</t>
-  </si>
-  <si>
-    <t>966504871256</t>
-  </si>
-  <si>
-    <t>1012636088</t>
-  </si>
-  <si>
-    <t>فهد بن عبدالعزيز بن حسن الرمضي</t>
-  </si>
-  <si>
-    <t>966548492992</t>
-  </si>
-  <si>
-    <t>1080086455</t>
-  </si>
-  <si>
-    <t>فهد بن ناصر بن عليان العليان</t>
-  </si>
-  <si>
-    <t>966536383338</t>
-  </si>
-  <si>
-    <t>1065885475</t>
-  </si>
-  <si>
-    <t>فهد عياد حمود الشمري</t>
-  </si>
-  <si>
-    <t>966505160121</t>
-  </si>
-  <si>
-    <t>1092783156</t>
-  </si>
-  <si>
-    <t>فهد محمد عبدالعزيز الصقعبي</t>
-  </si>
-  <si>
-    <t>1017302496</t>
-  </si>
-  <si>
-    <t>فهد نشمي نهير الغازي</t>
-  </si>
-  <si>
-    <t>966506180801</t>
-  </si>
-  <si>
-    <t>1015446717</t>
-  </si>
-  <si>
-    <t>فواز سعيد ابن عايض الحارثى</t>
-  </si>
-  <si>
-    <t>966500610040</t>
-  </si>
-  <si>
-    <t>1008416149</t>
-  </si>
-  <si>
-    <t>فيصل بن فهد بن سليمان الغربي</t>
-  </si>
-  <si>
-    <t>966544487744</t>
-  </si>
-  <si>
-    <t>1008525733</t>
-  </si>
-  <si>
-    <t>فيصل حمد جبر الرشيدي</t>
-  </si>
-  <si>
-    <t>966537347074</t>
-  </si>
-  <si>
-    <t>1047163306</t>
-  </si>
-  <si>
-    <t>ماجد ابراهيم دغفق الجروان</t>
-  </si>
-  <si>
-    <t>966567770295</t>
-  </si>
-  <si>
-    <t>1088649262</t>
-  </si>
-  <si>
-    <t>ماجد دغيم محمد الشمري</t>
-  </si>
-  <si>
-    <t>966503649509</t>
-  </si>
-  <si>
-    <t>1095649933</t>
-  </si>
-  <si>
-    <t>ماجد فهد مضحي المحمدي</t>
-  </si>
-  <si>
-    <t>966540800152</t>
-  </si>
-  <si>
-    <t>1087708275</t>
-  </si>
-  <si>
-    <t>ماهر مسلم عيد الذبياني</t>
-  </si>
-  <si>
-    <t>966550659309</t>
-  </si>
-  <si>
-    <t>1007872581</t>
-  </si>
-  <si>
-    <t>مجاهد عبد المحسن عبيد الجهني</t>
-  </si>
-  <si>
-    <t>966569159761</t>
-  </si>
-  <si>
-    <t>1075430155</t>
-  </si>
-  <si>
-    <t>محمد بن رشيد بن ساير الشمري</t>
-  </si>
-  <si>
-    <t>966551034502</t>
-  </si>
-  <si>
-    <t>1091277309</t>
-  </si>
-  <si>
-    <t>محمد بن ضيف الله بن دحيلان العلوي</t>
-  </si>
-  <si>
-    <t>966543989358</t>
-  </si>
-  <si>
-    <t>1011155460</t>
-  </si>
-  <si>
-    <t>محمد سعود بن جابر الهذلي</t>
-  </si>
-  <si>
-    <t>966533158676</t>
-  </si>
-  <si>
-    <t>1078487830</t>
-  </si>
-  <si>
-    <t>محمد مسعد رشيد المطيري</t>
-  </si>
-  <si>
-    <t>966531699404</t>
-  </si>
-  <si>
-    <t>1059142305</t>
-  </si>
-  <si>
-    <t>مشعل رشيد فالح الشمري</t>
-  </si>
-  <si>
-    <t>966566446649</t>
-  </si>
-  <si>
-    <t>1126563483</t>
-  </si>
-  <si>
-    <t>نادر بن غازي بن جمعان حماد الفريدي</t>
-  </si>
-  <si>
-    <t>966555156467</t>
-  </si>
-  <si>
     <t>Name_class</t>
   </si>
   <si>
@@ -376,6 +154,9 @@
   </si>
   <si>
     <t>حفظ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العمل الحالي </t>
   </si>
 </sst>
 </file>
@@ -469,14 +250,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -819,28 +600,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="6"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="6"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
+      <c r="B4" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -852,7 +633,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.71875" bestFit="1" customWidth="1"/>
@@ -860,296 +641,27 @@
     <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A48" t="s">
-        <v>13</v>
-      </c>
-      <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A49" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>19</v>
-      </c>
-      <c r="B50" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>22</v>
-      </c>
-      <c r="B51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>25</v>
-      </c>
-      <c r="B52" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>28</v>
-      </c>
-      <c r="B53" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>31</v>
-      </c>
-      <c r="B54" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A55" t="s">
-        <v>34</v>
-      </c>
-      <c r="B55" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55">
-        <v>966538218996</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" t="s">
-        <v>37</v>
-      </c>
-      <c r="C56" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C58" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A59" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>48</v>
-      </c>
-      <c r="B60" t="s">
-        <v>49</v>
-      </c>
-      <c r="C60" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" t="s">
-        <v>52</v>
-      </c>
-      <c r="C61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A62" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" t="s">
-        <v>55</v>
-      </c>
-      <c r="C62" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A63" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" t="s">
-        <v>58</v>
-      </c>
-      <c r="C63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A70" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" t="s">
-        <v>80</v>
+      <c r="E1" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A46:C70" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1163,8 +675,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>81</v>
+      <c r="A1" s="8" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1192,44 +704,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1241,7 +753,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1253,7 +765,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1265,7 +777,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1275,48 +787,48 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="3" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1328,7 +840,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1340,7 +852,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1352,7 +864,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1362,48 +874,48 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="3" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1415,7 +927,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1427,7 +939,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1439,7 +951,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1449,48 +961,48 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="3" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1502,7 +1014,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1514,7 +1026,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1526,7 +1038,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1536,48 +1048,48 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="3" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="A25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1589,7 +1101,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1601,7 +1113,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1613,7 +1125,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1623,7 +1135,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="3" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1647,89 +1159,89 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="5"/>
+      <c r="A1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="4"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>101</v>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1746,35 +1258,35 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>102</v>
+      <c r="A1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
